--- a/APM_files/152672346/Expedia ID 129109 Custom Name File.xlsx
+++ b/APM_files/152672346/Expedia ID 129109 Custom Name File.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11130"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/darkesthj/Dev/workspace/APM_files/152672346/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://dest1-my.sharepoint.com/personal/veronica_newman_coraltreeresidences_com/Documents/Expedia/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E2BB4E89-BBF4-FD4B-8C8E-7C9819926A3D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{3A174669-783E-4DE7-B825-460C889E4442}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{FB066D9F-75BE-4D3F-B368-ED2018897FF6}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="600" windowWidth="25600" windowHeight="26840" xr2:uid="{21B59805-2D6D-4DFB-9AB7-233FD7B7CE6F}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="51840" windowHeight="21120" xr2:uid="{21B59805-2D6D-4DFB-9AB7-233FD7B7CE6F}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -383,9 +383,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -721,19 +722,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2128D0B8-D076-4778-8DA5-5F09D4B2FCD3}">
   <dimension ref="A1:I89"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="15.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="19.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="37.6640625" style="1" customWidth="1"/>
-    <col min="6" max="6" width="20.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5" customWidth="1"/>
-    <col min="8" max="8" width="18.33203125" customWidth="1"/>
-    <col min="9" max="9" width="16.1640625" customWidth="1"/>
+    <col min="1" max="1" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="15.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="19.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="37.7109375" style="1" customWidth="1"/>
+    <col min="6" max="6" width="20.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" customWidth="1"/>
+    <col min="8" max="8" width="18.28515625" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>95</v>
       </c>
@@ -749,7 +750,7 @@
       <c r="E1" s="1" t="s">
         <v>93</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="2" t="s">
         <v>99</v>
       </c>
       <c r="G1" t="s">
@@ -762,7 +763,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -791,7 +792,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>0</v>
       </c>
@@ -820,7 +821,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>0</v>
       </c>
@@ -849,7 +850,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>0</v>
       </c>
@@ -878,7 +879,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>0</v>
       </c>
@@ -907,7 +908,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>0</v>
       </c>
@@ -936,7 +937,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>0</v>
       </c>
@@ -965,7 +966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>0</v>
       </c>
@@ -994,7 +995,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>0</v>
       </c>
@@ -1023,7 +1024,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>0</v>
       </c>
@@ -1052,7 +1053,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>0</v>
       </c>
@@ -1081,7 +1082,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>0</v>
       </c>
@@ -1110,7 +1111,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>0</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>0</v>
       </c>
@@ -1168,7 +1169,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>0</v>
       </c>
@@ -1197,7 +1198,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>0</v>
       </c>
@@ -1226,7 +1227,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>0</v>
       </c>
@@ -1255,7 +1256,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>0</v>
       </c>
@@ -1284,7 +1285,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>0</v>
       </c>
@@ -1313,7 +1314,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>0</v>
       </c>
@@ -1342,7 +1343,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>0</v>
       </c>
@@ -1371,7 +1372,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>0</v>
       </c>
@@ -1400,7 +1401,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>0</v>
       </c>
@@ -1429,7 +1430,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>0</v>
       </c>
@@ -1458,7 +1459,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>0</v>
       </c>
@@ -1487,7 +1488,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>0</v>
       </c>
@@ -1516,7 +1517,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>0</v>
       </c>
@@ -1545,7 +1546,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>0</v>
       </c>
@@ -1574,7 +1575,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>0</v>
       </c>
@@ -1603,7 +1604,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>0</v>
       </c>
@@ -1632,7 +1633,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>0</v>
       </c>
@@ -1661,7 +1662,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>0</v>
       </c>
@@ -1690,7 +1691,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>0</v>
       </c>
@@ -1719,7 +1720,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>0</v>
       </c>
@@ -1748,7 +1749,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>0</v>
       </c>
@@ -1777,7 +1778,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>0</v>
       </c>
@@ -1806,7 +1807,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>0</v>
       </c>
@@ -1835,7 +1836,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>0</v>
       </c>
@@ -1864,7 +1865,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>0</v>
       </c>
@@ -1893,7 +1894,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>0</v>
       </c>
@@ -1922,7 +1923,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>0</v>
       </c>
@@ -1951,7 +1952,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>0</v>
       </c>
@@ -1980,7 +1981,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>0</v>
       </c>
@@ -2009,7 +2010,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>0</v>
       </c>
@@ -2038,7 +2039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>0</v>
       </c>
@@ -2067,7 +2068,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>0</v>
       </c>
@@ -2096,7 +2097,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>0</v>
       </c>
@@ -2125,7 +2126,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>0</v>
       </c>
@@ -2154,7 +2155,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>0</v>
       </c>
@@ -2183,7 +2184,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>0</v>
       </c>
@@ -2212,7 +2213,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>0</v>
       </c>
@@ -2241,7 +2242,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>0</v>
       </c>
@@ -2270,7 +2271,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>0</v>
       </c>
@@ -2299,7 +2300,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>0</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>0</v>
       </c>
@@ -2357,7 +2358,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>0</v>
       </c>
@@ -2386,7 +2387,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>0</v>
       </c>
@@ -2415,7 +2416,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>0</v>
       </c>
@@ -2444,7 +2445,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>0</v>
       </c>
@@ -2473,7 +2474,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>0</v>
       </c>
@@ -2502,7 +2503,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>0</v>
       </c>
@@ -2531,7 +2532,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>0</v>
       </c>
@@ -2560,7 +2561,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>0</v>
       </c>
@@ -2589,7 +2590,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>0</v>
       </c>
@@ -2618,7 +2619,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>0</v>
       </c>
@@ -2647,7 +2648,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>0</v>
       </c>
@@ -2676,7 +2677,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>0</v>
       </c>
@@ -2705,7 +2706,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>0</v>
       </c>
@@ -2734,7 +2735,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>0</v>
       </c>
@@ -2763,7 +2764,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>0</v>
       </c>
@@ -2792,7 +2793,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>0</v>
       </c>
@@ -2821,7 +2822,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>0</v>
       </c>
@@ -2850,7 +2851,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>0</v>
       </c>
@@ -2879,7 +2880,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>0</v>
       </c>
@@ -2908,7 +2909,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>0</v>
       </c>
@@ -2937,7 +2938,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>0</v>
       </c>
@@ -2966,7 +2967,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>0</v>
       </c>
@@ -2995,7 +2996,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>0</v>
       </c>
@@ -3024,7 +3025,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>0</v>
       </c>
@@ -3053,7 +3054,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>0</v>
       </c>
@@ -3082,7 +3083,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>0</v>
       </c>
@@ -3111,7 +3112,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>0</v>
       </c>
@@ -3140,7 +3141,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>0</v>
       </c>
@@ -3169,7 +3170,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A85" t="s">
         <v>0</v>
       </c>
@@ -3198,7 +3199,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A86" t="s">
         <v>0</v>
       </c>
@@ -3227,7 +3228,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A87" t="s">
         <v>0</v>
       </c>
@@ -3256,7 +3257,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A88" t="s">
         <v>0</v>
       </c>
@@ -3285,7 +3286,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A89" t="s">
         <v>0</v>
       </c>
